--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554906293</v>
+        <v>46157.93111316415</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93111316415</v>
+        <v>46157.93135185002</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93135185002</v>
+        <v>46157.93383187006</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93383187006</v>
+        <v>46157.9369467124</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9369467124</v>
+        <v>46158.28204507125</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204507125</v>
+        <v>46158.29651596828</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29651596828</v>
+        <v>46158.29806533379</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806533379</v>
+        <v>46158.33369553667</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33369553667</v>
+        <v>46158.37221157685</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221157685</v>
+        <v>46158.37275081684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
